--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -3071,7 +3071,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보를 보기 전환으로 분리. 칸반 드래그 상태 변경, WBS 트리+상세, WBS 생성·수정·상태 변경·삭제 연결. docs/work-board-requirements-2026-07-01.md 기준.</t>
+          <t>실백엔드 데이터 검증 완료. 브랜드 상세페이지 룸의 WBS 10개·TODO 6개 기준으로 줄 목록, 선택 상세, 칸반 4열 전환 확인. 캡처: output/playwright/workboard-desktop-2026-07-01.png, workboard-kanban-desktop-2026-07-01.png</t>
         </is>
       </c>
     </row>
@@ -6153,12 +6153,12 @@
       </c>
       <c r="G13" s="216" t="inlineStr">
         <is>
-          <t>개선 반영</t>
+          <t>검증완료</t>
         </is>
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보 보기 전환 유지. 칸반은 Jira식 가로 보드+드래그 제거 영역으로 보강. WBS 항목 추가·수정·상태 변경·빈 항목 삭제를 wbsApi에 연결. 2026-07-01 탭별 헤더, LINE Seed 폰트 기준, 칼럼 폭/밀도 정리 반영. 후보 확정은 agent 화면 책임 유지.</t>
+          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세로 정리, 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인.</t>
         </is>
       </c>
     </row>
@@ -17070,7 +17070,7 @@
       </c>
       <c r="J103" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 WBS 줄 목록과 칸반 전환에서 실제 API 우선 사용. 2026-07-01 로컬 백엔드 데이터로 화면 검증 완료</t>
         </is>
       </c>
     </row>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="J106" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>WBS 줄 순서 변경 UI 유지. 같은 단계 재정렬 API 연결 상태로 검증</t>
         </is>
       </c>
     </row>
@@ -18464,7 +18464,7 @@
       </c>
       <c r="H130" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
       <c r="I130" s="304" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="J130" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>칸반 드래그/상태 버튼에서 PATCH /api/tasks/{taskId} 호출. 화면 검증 완료</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1733,6 +1733,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1763,6 +1764,7 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1958,6 +1960,7 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1992,6 +1995,7 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2063,6 +2067,7 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2150,6 +2155,7 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2237,6 +2243,7 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -3071,7 +3078,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>실백엔드 데이터 검증 완료. 브랜드 상세페이지 룸의 WBS 10개·TODO 6개 기준으로 줄 목록, 선택 상세, 칸반 4열 전환 확인. 캡처: output/playwright/workboard-desktop-2026-07-01.png, workboard-kanban-desktop-2026-07-01.png</t>
+          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
         </is>
       </c>
     </row>
@@ -4281,6 +4288,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -4402,6 +4410,7 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4484,6 +4493,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -5088,6 +5098,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6158,7 +6169,7 @@
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세로 정리, 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인.</t>
+          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
         </is>
       </c>
     </row>
@@ -6666,6 +6677,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -6826,6 +6838,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11326,6 +11339,7 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>
@@ -17070,7 +17084,7 @@
       </c>
       <c r="J103" s="304" t="inlineStr">
         <is>
-          <t>작업판 WBS 줄 목록과 칸반 전환에서 실제 API 우선 사용. 2026-07-01 로컬 백엔드 데이터로 화면 검증 완료</t>
+          <t>작업판 WBS 줄 목록, 하위 색 라인, 월/주/일 기간 보기, 칸반 전환에서 실제 API 우선 사용. dueAt 기준 기간 표시는 Google Calendar 연동 기준과 맞춤.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1733,6 +1733,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1763,6 +1764,7 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1958,6 +1960,7 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1992,6 +1995,7 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2063,6 +2067,7 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2150,6 +2155,7 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2237,6 +2243,7 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -3071,7 +3078,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보를 보기 전환으로 분리. 칸반 드래그 상태 변경, WBS 트리+상세, WBS 생성·수정·상태 변경·삭제 연결. docs/work-board-requirements-2026-07-01.md 기준.</t>
+          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
         </is>
       </c>
     </row>
@@ -4281,6 +4288,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -4402,6 +4410,7 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4484,6 +4493,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -5088,6 +5098,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6153,12 +6164,12 @@
       </c>
       <c r="G13" s="216" t="inlineStr">
         <is>
-          <t>개선 반영</t>
+          <t>검증완료</t>
         </is>
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보 보기 전환 유지. 칸반은 Jira식 가로 보드+드래그 제거 영역으로 보강. WBS 항목 추가·수정·상태 변경·빈 항목 삭제를 wbsApi에 연결. 2026-07-01 탭별 헤더, LINE Seed 폰트 기준, 칼럼 폭/밀도 정리 반영. 후보 확정은 agent 화면 책임 유지.</t>
+          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
         </is>
       </c>
     </row>
@@ -6666,6 +6677,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -6826,6 +6838,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11326,6 +11339,7 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>
@@ -17070,7 +17084,7 @@
       </c>
       <c r="J103" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 WBS 줄 목록, 하위 색 라인, 월/주/일 기간 보기, 칸반 전환에서 실제 API 우선 사용. dueAt 기준 기간 표시는 Google Calendar 연동 기준과 맞춤.</t>
         </is>
       </c>
     </row>
@@ -17226,7 +17240,7 @@
       </c>
       <c r="J106" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>WBS 줄 순서 변경 UI 유지. 같은 단계 재정렬 API 연결 상태로 검증</t>
         </is>
       </c>
     </row>
@@ -18464,7 +18478,7 @@
       </c>
       <c r="H130" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
       <c r="I130" s="304" t="inlineStr">
@@ -18474,7 +18488,7 @@
       </c>
       <c r="J130" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>칸반 드래그/상태 버튼에서 PATCH /api/tasks/{taskId} 호출. 화면 검증 완료</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1733,7 +1733,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1764,7 +1763,6 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1960,7 +1958,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1995,7 +1992,6 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2067,7 +2063,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2155,7 +2150,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2243,7 +2237,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -2857,7 +2850,7 @@
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>POST /project-rooms · /resources · /ai/*</t>
+          <t>POST /api/project-rooms · POST /api/resources · POST /api/ai/review-contract-documents</t>
         </is>
       </c>
       <c r="F11" s="64" t="inlineStr">
@@ -2877,7 +2870,7 @@
       </c>
       <c r="I11" s="64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>부분(로컬 UI 검증 완료)</t>
         </is>
       </c>
       <c r="J11" s="24" t="inlineStr">
@@ -2892,7 +2885,7 @@
       </c>
       <c r="L11" s="25" t="inlineStr">
         <is>
-          <t>업로드+분석 트리거</t>
+          <t>2026-07-02 local seed 토큰 로그인 → /api/me 200 → UI에서 POST /api/project-rooms 200 → 새 룸 상세 이동 확인. 자료 업로드/에이전트 검토 실패는 부분 성공으로 노출.</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4403,6 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4493,7 +4485,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -4815,12 +4806,12 @@
       </c>
       <c r="C3" s="88" t="inlineStr">
         <is>
-          <t>완료: apiRequest Bearer 주입 + access/refresh 저장 + 401 단일 refresh 재시도 + 구글 콜백/logout</t>
+          <t>완료: apiRequest Bearer 주입 + access/refresh 저장 + 401 단일 refresh 재시도 + 구글 콜백/logout + 로컬 개발 토큰 로그인</t>
         </is>
       </c>
       <c r="D3" s="89" t="inlineStr">
         <is>
-          <t>apiRequest에 Bearer 헤더 주입 + 토큰 저장소(인메모리) + 401시 refresh 재발급</t>
+          <t>apiRequest Bearer 헤더 유지. 로컬은 seed access token으로 /api/me 세션을 만들고 실제 API 버튼 흐름을 검증한다.</t>
         </is>
       </c>
       <c r="E3" s="149" t="inlineStr">
@@ -5000,7 +4991,7 @@
       </c>
       <c r="C8" s="96" t="inlineStr">
         <is>
-          <t>프론트 콜백·토큰저장 완료. redirectUri 등록 + 실 로그인 왕복은 수동 검증 남음</t>
+          <t>프론트 콜백·토큰저장 완료. 로컬 개발 토큰 로그인으로 실제 API 세션 검증 가능. Google redirectUri 등록/실 왕복은 수동 검증 남음</t>
         </is>
       </c>
       <c r="D8" s="97" t="inlineStr">
@@ -5098,7 +5089,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6023,7 +6013,7 @@
       </c>
       <c r="D10" s="89" t="inlineStr">
         <is>
-          <t>룸 생성·업로드·계약서분석</t>
+          <t>룸 생성·자료 업로드·에이전트 자료 검토</t>
         </is>
       </c>
       <c r="E10" s="89" t="inlineStr">
@@ -6038,12 +6028,12 @@
       </c>
       <c r="G10" s="125" t="inlineStr">
         <is>
-          <t>확인예정</t>
+          <t>검증완료</t>
         </is>
       </c>
       <c r="H10" s="89" t="inlineStr">
         <is>
-          <t>디자인 상태 미확인</t>
+          <t>로컬 seed 사용자로 로그인 화면 개발 토큰 접속, 프로젝트룸 생성 버튼, POST /api/project-rooms 200, 상세 이동까지 확인. 자료 후속 실패는 사용자에게 표시.</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6828,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11339,7 +11328,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>
@@ -15680,7 +15668,7 @@
       </c>
       <c r="J76" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-02 local seed JWT로 로그인 화면 개발 접속 후 UI 생성 200 확인. /app/project-rooms/new 생성 버튼 연결 상태.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1733,7 +1733,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1764,7 +1763,6 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1960,7 +1958,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1995,7 +1992,6 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2067,7 +2063,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2155,7 +2150,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2243,7 +2237,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -4410,7 +4403,6 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4493,7 +4485,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -5098,7 +5089,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6838,7 +6828,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11339,7 +11328,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>
@@ -17084,7 +17072,7 @@
       </c>
       <c r="J103" s="304" t="inlineStr">
         <is>
-          <t>작업판 WBS 줄 목록, 하위 색 라인, 월/주/일 기간 보기, 칸반 전환에서 실제 API 우선 사용. dueAt 기준 기간 표시는 Google Calendar 연동 기준과 맞춤.</t>
+          <t>작업판 WBS 줄 목록, 하위 색 라인, 월/주/일 기간 보기, 칸반 전환 기준 유지. 2026-07-02 보기 순서와 카드 줄바꿈 보강.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1733,7 +1733,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1764,7 +1763,6 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1960,7 +1958,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1995,7 +1992,6 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2067,7 +2063,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2155,7 +2150,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2243,7 +2237,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -3011,7 +3004,7 @@
       </c>
       <c r="K13" s="202" t="inlineStr">
         <is>
-          <t>됨</t>
+          <t>됨 / 2026-07-02 목업/하드코딩 감사 반영: MOCK_FLOW export 제거, ResourceFlowView 기본 빈 상태 전환, 랜딩/앱 설명의 개발자 문구 제거, 소통 컴포넌트는 팀원 작업 범위라 별도 처리 대기.</t>
         </is>
       </c>
       <c r="L13" s="25" t="inlineStr">
@@ -3215,7 +3208,7 @@
       </c>
       <c r="K17" s="202" t="inlineStr">
         <is>
-          <t>됨</t>
+          <t>됨 / 2026-07-02 목업/하드코딩 감사 반영: MOCK_FLOW export 제거, ResourceFlowView 기본 빈 상태 전환, 랜딩/앱 설명의 개발자 문구 제거, 소통 컴포넌트는 팀원 작업 범위라 별도 처리 대기.</t>
         </is>
       </c>
       <c r="L17" s="25" t="inlineStr">
@@ -3605,7 +3598,7 @@
       </c>
       <c r="K24" s="202" t="inlineStr">
         <is>
-          <t>됨</t>
+          <t>됨 / 2026-07-02 목업/하드코딩 감사 반영: MOCK_FLOW export 제거, ResourceFlowView 기본 빈 상태 전환, 랜딩/앱 설명의 개발자 문구 제거, 소통 컴포넌트는 팀원 작업 범위라 별도 처리 대기.</t>
         </is>
       </c>
       <c r="L24" s="25" t="inlineStr">
@@ -3685,7 +3678,7 @@
       </c>
       <c r="K26" s="202" t="inlineStr">
         <is>
-          <t>됨</t>
+          <t>됨 / 2026-07-02 목업/하드코딩 감사 반영: MOCK_FLOW export 제거, ResourceFlowView 기본 빈 상태 전환, 랜딩/앱 설명의 개발자 문구 제거, 소통 컴포넌트는 팀원 작업 범위라 별도 처리 대기.</t>
         </is>
       </c>
       <c r="L26" s="25" t="inlineStr">
@@ -3747,7 +3740,7 @@
       </c>
       <c r="K27" s="202" t="inlineStr">
         <is>
-          <t>됨</t>
+          <t>됨 / 2026-07-02 목업/하드코딩 감사 반영: MOCK_FLOW export 제거, ResourceFlowView 기본 빈 상태 전환, 랜딩/앱 설명의 개발자 문구 제거, 소통 컴포넌트는 팀원 작업 범위라 별도 처리 대기.</t>
         </is>
       </c>
       <c r="L27" s="25" t="inlineStr">
@@ -3809,7 +3802,7 @@
       </c>
       <c r="K28" s="203" t="inlineStr">
         <is>
-          <t>부분</t>
+          <t>부분 / 2026-07-02 목업/하드코딩 감사 반영: MOCK_FLOW export 제거, ResourceFlowView 기본 빈 상태 전환, 랜딩/앱 설명의 개발자 문구 제거, 소통 컴포넌트는 팀원 작업 범위라 별도 처리 대기.</t>
         </is>
       </c>
       <c r="L28" s="25" t="inlineStr">
@@ -3889,7 +3882,7 @@
       </c>
       <c r="K30" s="203" t="inlineStr">
         <is>
-          <t>부분</t>
+          <t>부분 / 2026-07-02 목업/하드코딩 감사 반영: MOCK_FLOW export 제거, ResourceFlowView 기본 빈 상태 전환, 랜딩/앱 설명의 개발자 문구 제거, 소통 컴포넌트는 팀원 작업 범위라 별도 처리 대기.</t>
         </is>
       </c>
       <c r="L30" s="25" t="inlineStr">
@@ -4410,7 +4403,6 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4493,7 +4485,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -5098,7 +5089,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6677,7 +6667,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -6838,7 +6827,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11339,7 +11327,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1733,6 +1733,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1763,6 +1764,7 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1879,12 +1881,12 @@
       </c>
       <c r="C12" s="203" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="D12" s="285" t="inlineStr">
         <is>
-          <t>401은 로그인 필요, 실패/데이터 없음은 empty/offline, 쓰기 액션의 가짜 성공 데이터 제거</t>
+          <t>대부분 화면 loading/error/fallback(추정) + Gemini 감사 기준 사용자 노출 샘플/개발자 용어 추가 정리</t>
         </is>
       </c>
       <c r="E12" s="232" t="n"/>
@@ -1958,6 +1960,7 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1992,6 +1995,7 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2063,6 +2067,7 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2150,6 +2155,7 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2237,6 +2243,7 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -4281,7 +4288,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1733,7 +1733,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1764,7 +1763,6 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1960,7 +1958,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1995,7 +1992,6 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2067,7 +2063,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2155,7 +2150,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2243,7 +2237,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -2857,7 +2850,7 @@
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>POST /project-rooms · /resources · /ai/*</t>
+          <t>POST /api/project-rooms · POST /api/resources · POST /api/ai/review-contract-documents</t>
         </is>
       </c>
       <c r="F11" s="64" t="inlineStr">
@@ -2892,7 +2885,7 @@
       </c>
       <c r="L11" s="25" t="inlineStr">
         <is>
-          <t>업로드+분석 트리거</t>
+          <t>2026-07-02 로컬 백엔드 POST 200 + Playwright 상단 프로젝트룸 패널 생성/상세 이동 검증 완료. 생성 실패 메시지 표시, 버튼 이름 충돌 제거. 자료 첨부 시 업로드와 에이전트 후보 생성은 자료보드에서 이어감.</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4281,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -4410,7 +4402,6 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4493,7 +4484,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -5098,7 +5088,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6023,12 +6012,12 @@
       </c>
       <c r="D10" s="89" t="inlineStr">
         <is>
-          <t>룸 생성·업로드·계약서분석</t>
+          <t>룸 생성·자료 업로드·에이전트 후보</t>
         </is>
       </c>
       <c r="E10" s="89" t="inlineStr">
         <is>
-          <t>create+upload+reviewContractDocuments</t>
+          <t>projectRoomApi.create + resourcesApi.upload + agentApi 후보 생성</t>
         </is>
       </c>
       <c r="F10" s="215" t="inlineStr">
@@ -6038,12 +6027,12 @@
       </c>
       <c r="G10" s="125" t="inlineStr">
         <is>
-          <t>확인예정</t>
+          <t>검증완료</t>
         </is>
       </c>
       <c r="H10" s="89" t="inlineStr">
         <is>
-          <t>디자인 상태 미확인</t>
+          <t>2026-07-02 로컬 백엔드 POST 200 + Playwright 상단 프로젝트룸 패널 생성/상세 이동 검증 완료.</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6827,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11339,7 +11327,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 명세 맵핑" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드 카드 후보" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 용도·화면·위젯 맵" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="품질 감사" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1932,7 +1933,7 @@
       </c>
       <c r="D14" s="285" t="inlineStr">
         <is>
-          <t>typecheck 통과 · tauri/product/diff 재검증 예정 · 최신 API 경로 정정</t>
+          <t>typecheck 통과 · tauri/product/diff 재검증 예정 · 최신 API 경로 정정 · 목업/하드코딩 감사 키워드 정리</t>
         </is>
       </c>
       <c r="E14" s="232" t="n"/>
@@ -1960,7 +1961,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1995,7 +1995,6 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2067,7 +2066,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2155,7 +2153,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2243,7 +2240,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -2331,6 +2327,84 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>다음 작업</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>목업·하드코딩 데이터</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>프로덕션 src</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-07-02 Gemini 감사 반영: 프로덕션 src에서 계약/개인명/mock/배포된 내부문구 검색 0건. ResourceFlowView 기본 목업 제거, 공개/위젯 개발자 문구 사용자 관점으로 정리. Storybook/test는 감사 제외.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Storybook/test 예시는 별도 QA에서 유지 여부 판단</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4288,7 +4362,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -4410,7 +4483,6 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4493,7 +4565,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -5098,7 +5169,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6677,7 +6747,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -6838,7 +6907,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11339,7 +11407,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1722,7 +1722,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="192" t="inlineStr">
         <is>
-          <t>Bubli 프론트엔드 진행 요약 · 2026-07-01 (목업 제거·최신 백엔드 #145·API 용도맵 반영)</t>
+          <t>Bubli 프론트엔드 진행 요약 · 2026-07-01 (목업 제거·구글 로그인 호환 경로 반영)</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1764,7 +1763,6 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1960,7 +1958,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -1990,12 +1987,11 @@
       </c>
       <c r="D18" s="285" t="inlineStr">
         <is>
-          <t>백엔드 최신 동기화·Docker DB/Redis 기동 확인. 인증 세션 없는 route smoke는 로그인/401 리다이렉트까지 확인</t>
+          <t>백엔드 최신 동기화·Docker DB/Redis 기동 확인. 인증 세션 없는 route smoke는 로그인/401 리다이렉트까지 확인. 구버전 Google OAuth 진입 경로 404 방지 추가.</t>
         </is>
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2067,7 +2063,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2155,7 +2150,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2243,7 +2237,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -2280,7 +2273,7 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="287" t="inlineStr">
         <is>
-          <t>· 배포 실동작은 구글 OAuth 실계정, WebSocket/LiveKit, Tauri 네이티브 런타임만 수동 검증 남음. 인증 없는 smoke는 /login 리다이렉트와 401 확인.</t>
+          <t>· 배포 실동작은 구글 OAuth 실계정, WebSocket/LiveKit, Tauri 네이티브 런타임만 수동 검증 남음. /oauth2/authorization/google 호환 진입은 프론트 route smoke로 확인.</t>
         </is>
       </c>
       <c r="B41" s="20" t="n"/>
@@ -2635,7 +2628,7 @@
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>구글 OAuth 진입</t>
+          <t>구글 OAuth 진입 · /oauth2/authorization/google 호환 라우트</t>
         </is>
       </c>
       <c r="F6" s="64" t="inlineStr">
@@ -2660,7 +2653,7 @@
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>일치</t>
+          <t>일치 · 2026-07-02: /oauth2/authorization/google 호환 진입 추가로 이전 링크 404 방지</t>
         </is>
       </c>
       <c r="K6" s="202" t="inlineStr">
@@ -4288,7 +4281,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -4410,7 +4402,6 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="232" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="291" t="inlineStr">
         <is>
@@ -4493,7 +4484,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="291" t="inlineStr">
         <is>
@@ -5000,12 +4990,12 @@
       </c>
       <c r="C8" s="96" t="inlineStr">
         <is>
-          <t>프론트 콜백·토큰저장 완료. redirectUri 등록 + 실 로그인 왕복은 수동 검증 남음</t>
+          <t>프론트 콜백·토큰저장 완료. /oauth2/authorization/google 호환 진입 추가. redirectUri 실계정 왕복은 수동 검증 남음</t>
         </is>
       </c>
       <c r="D8" s="97" t="inlineStr">
         <is>
-          <t>구글 콘솔에 배포 redirectUri 등록 + 프론트가 같은 redirectUri 전송 + 응답 accessToken 저장</t>
+          <t>구글 콘솔에 배포 redirectUri 등록 + 프론트가 같은 redirectUri 전송 + 응답 accessToken 저장 + 이전 OAuth 진입 URL 404 방지</t>
         </is>
       </c>
       <c r="E8" s="152" t="inlineStr">
@@ -5098,7 +5088,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -5855,12 +5844,12 @@
       </c>
       <c r="D6" s="89" t="inlineStr">
         <is>
-          <t>구글 OAuth 시작 URL</t>
+          <t>구글 OAuth 시작 URL + 구버전 OAuth 진입 호환</t>
         </is>
       </c>
       <c r="E6" s="89" t="inlineStr">
         <is>
-          <t>getGoogleAuthorizationUrl</t>
+          <t>getGoogleAuthorizationUrl · /oauth2/authorization/google</t>
         </is>
       </c>
       <c r="F6" s="215" t="inlineStr">
@@ -5875,7 +5864,7 @@
       </c>
       <c r="H6" s="89" t="inlineStr">
         <is>
-          <t>디자인 완료 · 반응형 미확인</t>
+          <t>디자인 완료 · 반응형 미확인 · 이전 OAuth URL 404 방지 추가</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6666,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -7403,7 +7391,7 @@
       </c>
       <c r="F27" s="215" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터 · 호환 route 연결</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11327,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>
@@ -12696,7 +12683,7 @@
       </c>
       <c r="F19" s="304" t="inlineStr">
         <is>
-          <t>/login, /auth/callback, /app 상단바, /app/settings</t>
+          <t>/login, /oauth2/authorization/google, /auth/callback, /app 상단바, /app/settings</t>
         </is>
       </c>
       <c r="G19" s="304" t="inlineStr">
@@ -12706,7 +12693,7 @@
       </c>
       <c r="H19" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
       <c r="I19" s="304" t="inlineStr">
@@ -12716,7 +12703,7 @@
       </c>
       <c r="J19" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>현재 화면에서 실제 API 우선 사용. 이전 OAuth URL은 호환 route로 authorize API에 연결</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -156,7 +156,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -266,6 +266,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EADCF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -549,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1402,6 +1407,9 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -1709,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2287,6 +2295,13 @@
       <c r="C41" s="20" t="n"/>
       <c r="D41" s="20" t="n"/>
       <c r="E41" s="232" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="310" t="inlineStr">
+        <is>
+          <t>· 2026-07-02 목업/하드코딩 카피 정리: 프로덕션 코드의 MOCK 식별자, 특정 인명, 계약/계약서 표현, 배포/릴리스 개발자 문구를 사용자 관점 표현으로 교정. Storybook/test/dev fallback은 제외.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -4288,7 +4303,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -4391,7 +4405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4725,6 +4739,30 @@
         </is>
       </c>
       <c r="D20" s="275" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="311" t="inlineStr">
+        <is>
+          <t>방금 완료 (Codex 목업·하드코딩 문구 정리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>목업/하드코딩 정리</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>프로덕션 코드에서 명시적 MOCK_FLOW, 특정 이름, 계약/계약서, 배포/릴리스 개발자 문구 제거. Storybook/test/dev fallback 제외.</t>
+        </is>
+      </c>
+      <c r="D23" s="312" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -5098,7 +5136,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
         <is>
@@ -6677,7 +6714,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -6838,7 +6874,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11339,7 +11374,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
+          <t>WBS/칸반/후보를 보기 전환으로 분리. 칸반 드래그 상태 변경, WBS 줄 목록+상세, WBS 생성·수정·상태 변경·삭제 연결. WBS 줄 목록은 Jira식 색 줄, 하위 단계 표시, 사용자 지정 줄 색을 보강. 2026-07-01 Playwright로 WBS 줄 추가 POST와 상태 변경 PATCH 검증 완료. docs/work-board-requirements-2026-07-01.md 기준.</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
+          <t>WBS/칸반/후보 보기 전환 유지. 칸반은 Jira식 가로 보드+드래그 제거 영역으로 보강. WBS 항목 추가·수정·상태 변경·빈 항목 삭제를 wbsApi에 연결. WBS 줄 목록은 색 줄과 하위 단계 표기를 보강하고 사용자가 줄 색을 직접 바꿀 수 있게 유지. 2026-07-01 Playwright로 WBS 줄 추가 POST, 상태 변경 PATCH, WBS/칸반/후보 탭 전환 검증 완료. 후보 확정은 agent 화면 책임 유지.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -3464,7 +3464,7 @@
       </c>
       <c r="I22" s="64" t="inlineStr">
         <is>
-          <t>부분(후보 생성 실데이터 필요)</t>
+          <t>부분(작업판 후보 생성 버튼 연결, 실계정 검증 필요)</t>
         </is>
       </c>
       <c r="J22" s="24" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="L22" s="25" t="inlineStr">
         <is>
-          <t>최신 백엔드 #143-#145 API 래퍼 추가. 화면은 기존 후보함 중심, 생성문서/확정요구사항은 API어댑터 준비.</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. 실계정 job 생성 성공 응답과 후보 반영 검증은 후속.</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6667,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -6828,6 +6827,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F21" s="215" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+작업판 버튼</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="F22" s="215" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+작업판 버튼</t>
         </is>
       </c>
     </row>
@@ -11328,6 +11328,7 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>
@@ -12434,7 +12435,7 @@
       </c>
       <c r="H14" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+화면연결</t>
         </is>
       </c>
       <c r="I14" s="304" t="inlineStr">
@@ -12444,7 +12445,7 @@
       </c>
       <c r="J14" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. 실계정 job 생성 성공 응답과 후보 반영 검증은 후속.</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12487,7 @@
       </c>
       <c r="H15" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+화면연결</t>
         </is>
       </c>
       <c r="I15" s="304" t="inlineStr">
@@ -12496,7 +12497,7 @@
       </c>
       <c r="J15" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. 실계정 job 생성 성공 응답과 후보 반영 검증은 후속.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 명세 맵핑" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드 카드 후보" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 용도·화면·위젯 맵" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작업판 후보·일정 삭제" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -155,8 +156,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002C3540"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -266,6 +271,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EADCF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7EAF4"/>
       </patternFill>
     </fill>
   </fills>
@@ -549,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="311">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1400,6 +1410,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2324,6 +2337,273 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="304" t="inlineStr">
+        <is>
+          <t>갱신일</t>
+        </is>
+      </c>
+      <c r="B1" s="304" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C1" s="304" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="D1" s="304" t="inlineStr">
+        <is>
+          <t>프로젝트룸 WBS/칸반 후보 생성과 WBS 일정 삭제</t>
+        </is>
+      </c>
+      <c r="E1" s="304" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="304" t="n"/>
+      <c r="B2" s="304" t="n"/>
+      <c r="C2" s="304" t="n"/>
+      <c r="D2" s="304" t="n"/>
+      <c r="E2" s="304" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="310" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="310" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="C3" s="310" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D3" s="310" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="E3" s="310" t="inlineStr">
+        <is>
+          <t>검증/규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="304" t="inlineStr">
+        <is>
+          <t>WBS 후보 생성</t>
+        </is>
+      </c>
+      <c r="B4" s="304" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C4" s="304" t="inlineStr">
+        <is>
+          <t>POST /api/ai/generate-wbs</t>
+        </is>
+      </c>
+      <c r="D4" s="304" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E4" s="304" t="inlineStr">
+        <is>
+          <t>버튼 클릭 후 DRAFT WBS 후보 재조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="304" t="inlineStr">
+        <is>
+          <t>칸반 후보 생성</t>
+        </is>
+      </c>
+      <c r="B5" s="304" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C5" s="304" t="inlineStr">
+        <is>
+          <t>POST /api/ai/generate-tasks</t>
+        </is>
+      </c>
+      <c r="D5" s="304" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E5" s="304" t="inlineStr">
+        <is>
+          <t>버튼 클릭 후 DRAFT TASK/TODO 후보 재조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="304" t="inlineStr">
+        <is>
+          <t>후보 조회</t>
+        </is>
+      </c>
+      <c r="B6" s="304" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C6" s="304" t="inlineStr">
+        <is>
+          <t>GET /api/project-rooms/{roomId}/agent/suggestions</t>
+        </is>
+      </c>
+      <c r="D6" s="304" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E6" s="304" t="inlineStr">
+        <is>
+          <t>WBS/TASK/TODO 타입별로 후보 트레이 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="304" t="inlineStr">
+        <is>
+          <t>후보 처리</t>
+        </is>
+      </c>
+      <c r="B7" s="304" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C7" s="304" t="inlineStr">
+        <is>
+          <t>PATCH /api/agent/suggestions/{id}</t>
+        </is>
+      </c>
+      <c r="D7" s="304" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E7" s="304" t="inlineStr">
+        <is>
+          <t>승인 시 작업판 다시 조회, 보류/제외 시 후보 목록 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="304" t="inlineStr">
+        <is>
+          <t>WBS 기간 저장</t>
+        </is>
+      </c>
+      <c r="B8" s="304" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C8" s="304" t="inlineStr">
+        <is>
+          <t>POST/PATCH /api/schedules</t>
+        </is>
+      </c>
+      <c r="D8" s="304" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E8" s="304" t="inlineStr">
+        <is>
+          <t>간트 바 생성·이동·길이 조절이 일정 row와 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="304" t="inlineStr">
+        <is>
+          <t>WBS 기간 초기화</t>
+        </is>
+      </c>
+      <c r="B9" s="304" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C9" s="304" t="inlineStr">
+        <is>
+          <t>DELETE /api/schedules/{scheduleId}</t>
+        </is>
+      </c>
+      <c r="D9" s="304" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E9" s="304" t="inlineStr">
+        <is>
+          <t>서버 삭제 성공 후 화면 기간 제거. 실패 시 화면 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="304" t="inlineStr">
+        <is>
+          <t>WBS 삭제</t>
+        </is>
+      </c>
+      <c r="B10" s="304" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C10" s="304" t="inlineStr">
+        <is>
+          <t>DELETE /api/schedules/{scheduleId} -&gt; DELETE /api/wbs-items/{id}</t>
+        </is>
+      </c>
+      <c r="D10" s="304" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E10" s="304" t="inlineStr">
+        <is>
+          <t>연결 일정 삭제 성공 후 WBS 삭제. 실패 시 화면과 DB를 둘 다 유지</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3031,12 +3311,12 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>wbsApi(+agent+projectRoom)</t>
+          <t>wbsApi+todoApi+calendarApi+agentApi</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>GET /wbs-board · /wbs-items · POST /wbs-items · PATCH /wbs-items/{id} · DELETE /wbs-items/{id} · reorder</t>
+          <t>GET /wbs-board · /wbs-items · POST/PATCH/DELETE /wbs-items · POST/PATCH/DELETE /api/schedules · POST /api/ai/generate-wbs · POST /api/ai/generate-tasks · GET /project-rooms/{id}/agent/suggestions · PATCH /agent/suggestions/{id}</t>
         </is>
       </c>
       <c r="F14" s="64" t="inlineStr">
@@ -3071,7 +3351,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
+          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-03 WBS 후보 생성은 agentApi.generateWbs, 칸반 후보 생성은 agentApi.generateTasks에 연결. 후보 목록/승인·보류·제외는 /api/project-rooms/{roomId}/agent/suggestions와 /api/agent/suggestions/{id} 사용. WBS 기간 생성/수정/초기화/삭제는 /api/schedules를 사용하고, 삭제는 백엔드의 Google Calendar 동기화 삭제와 DB 삭제 성공 후 화면에서 제거.</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3744,7 @@
       </c>
       <c r="I22" s="64" t="inlineStr">
         <is>
-          <t>부분(작업판 후보 생성 버튼 연결, 실계정 검증 필요)</t>
+          <t>부분(실계정 검증 필요)</t>
         </is>
       </c>
       <c r="J22" s="24" t="inlineStr">
@@ -3479,7 +3759,7 @@
       </c>
       <c r="L22" s="25" t="inlineStr">
         <is>
-          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. 실계정 job 생성 성공 응답과 후보 반영 검증은 후속.</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. DRAFT 후보 목록을 불러오고 승인·보류·제외를 PATCH /api/agent/suggestions/{id}로 처리.</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4561,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -10468,7 +10747,7 @@
       </c>
       <c r="F154" s="216" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12412,7 @@
       </c>
       <c r="J8" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 후보 트레이에서 DRAFT 후보 조회와 승인·보류·제외 액션으로 사용.</t>
         </is>
       </c>
     </row>
@@ -12185,7 +12464,7 @@
       </c>
       <c r="J9" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 후보 트레이에서 DRAFT 후보 조회와 승인·보류·제외 액션으로 사용.</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12724,7 @@
       </c>
       <c r="J14" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. 실계정 job 생성 성공 응답과 후보 반영 검증은 후속.</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에 WBS 후보 생성, 칸반 후보 생성 버튼 연결. 생성 후 DRAFT 후보 목록을 다시 조회.</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12776,7 @@
       </c>
       <c r="J15" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. 실계정 job 생성 성공 응답과 후보 반영 검증은 후속.</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에 WBS 후보 생성, 칸반 후보 생성 버튼 연결. 생성 후 DRAFT 후보 목록을 다시 조회.</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16364,7 @@
       </c>
       <c r="J84" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 후보 트레이에서 DRAFT 후보 조회와 승인·보류·제외 액션으로 사용.</t>
         </is>
       </c>
     </row>
@@ -18093,7 +18372,7 @@
       </c>
       <c r="F123" s="304" t="inlineStr">
         <is>
-          <t>/app/calendar, /app/project-rooms/{roomId}, 일정 버블</t>
+          <t>/app/calendar, /app/project-rooms/{roomId}/work, 일정 버블</t>
         </is>
       </c>
       <c r="G123" s="304" t="inlineStr">
@@ -18113,7 +18392,7 @@
       </c>
       <c r="J123" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>WBS 기간 바 생성·이동·길이 조절에서 일정 row를 생성/수정해 Google Calendar 동기화 기준으로 사용.</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18424,7 @@
       </c>
       <c r="F124" s="304" t="inlineStr">
         <is>
-          <t>/app/calendar, /app/project-rooms/{roomId}, 일정 버블</t>
+          <t>/app/calendar, /app/project-rooms/{roomId}/work, 일정 버블</t>
         </is>
       </c>
       <c r="G124" s="304" t="inlineStr">
@@ -18155,7 +18434,7 @@
       </c>
       <c r="H124" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
       <c r="I124" s="304" t="inlineStr">
@@ -18165,7 +18444,7 @@
       </c>
       <c r="J124" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 WBS 기간 초기화와 WBS 삭제에서 /api/schedules/{scheduleId}를 먼저 호출. 백엔드가 Google Calendar 이벤트와 DB row를 지우며, 성공 후 화면에서 제거.</t>
         </is>
       </c>
     </row>
@@ -18197,7 +18476,7 @@
       </c>
       <c r="F125" s="304" t="inlineStr">
         <is>
-          <t>/app/calendar, /app/project-rooms/{roomId}, 일정 버블</t>
+          <t>/app/calendar, /app/project-rooms/{roomId}/work, 일정 버블</t>
         </is>
       </c>
       <c r="G125" s="304" t="inlineStr">
@@ -18207,7 +18486,7 @@
       </c>
       <c r="H125" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
       <c r="I125" s="304" t="inlineStr">
@@ -18217,7 +18496,7 @@
       </c>
       <c r="J125" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>WBS 기간 바 생성·이동·길이 조절에서 일정 row를 생성/수정해 Google Calendar 동기화 기준으로 사용.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -161,7 +161,7 @@
       <color rgb="002C3540"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -278,8 +278,13 @@
         <fgColor rgb="00D7EAF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border/>
     <border>
       <left style="thin">
@@ -555,11 +560,19 @@
         <color rgb="FFCDD8DF"/>
       </right>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="311">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1413,6 +1426,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2343,14 +2365,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2371,7 +2393,7 @@
       </c>
       <c r="D1" s="304" t="inlineStr">
         <is>
-          <t>프로젝트룸 WBS/칸반 후보 생성과 WBS 일정 삭제</t>
+          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화</t>
         </is>
       </c>
       <c r="E1" s="304" t="n"/>
@@ -2384,218 +2406,299 @@
       <c r="E2" s="304" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="310" t="inlineStr">
+      <c r="A3" s="311" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B3" s="310" t="inlineStr">
+      <c r="B3" s="311" t="inlineStr">
         <is>
           <t>화면</t>
         </is>
       </c>
-      <c r="C3" s="310" t="inlineStr">
+      <c r="C3" s="311" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D3" s="310" t="inlineStr">
+      <c r="D3" s="311" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E3" s="310" t="inlineStr">
+      <c r="E3" s="311" t="inlineStr">
         <is>
           <t>검증/규칙</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="304" t="inlineStr">
+      <c r="A4" s="312" t="inlineStr">
         <is>
           <t>WBS 후보 생성</t>
         </is>
       </c>
-      <c r="B4" s="304" t="inlineStr">
+      <c r="B4" s="312" t="inlineStr">
         <is>
           <t>/app/project-rooms/{roomId}/work</t>
         </is>
       </c>
-      <c r="C4" s="304" t="inlineStr">
+      <c r="C4" s="312" t="inlineStr">
         <is>
           <t>POST /api/ai/generate-wbs</t>
         </is>
       </c>
-      <c r="D4" s="304" t="inlineStr">
+      <c r="D4" s="312" t="inlineStr">
         <is>
           <t>연결</t>
         </is>
       </c>
-      <c r="E4" s="304" t="inlineStr">
+      <c r="E4" s="312" t="inlineStr">
         <is>
           <t>버튼 클릭 후 DRAFT WBS 후보 재조회</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="304" t="inlineStr">
+      <c r="A5" s="312" t="inlineStr">
         <is>
           <t>칸반 후보 생성</t>
         </is>
       </c>
-      <c r="B5" s="304" t="inlineStr">
+      <c r="B5" s="312" t="inlineStr">
         <is>
           <t>/app/project-rooms/{roomId}/work</t>
         </is>
       </c>
-      <c r="C5" s="304" t="inlineStr">
+      <c r="C5" s="312" t="inlineStr">
         <is>
           <t>POST /api/ai/generate-tasks</t>
         </is>
       </c>
-      <c r="D5" s="304" t="inlineStr">
+      <c r="D5" s="312" t="inlineStr">
         <is>
           <t>연결</t>
         </is>
       </c>
-      <c r="E5" s="304" t="inlineStr">
+      <c r="E5" s="312" t="inlineStr">
         <is>
           <t>버튼 클릭 후 DRAFT TASK/TODO 후보 재조회</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="304" t="inlineStr">
+      <c r="A6" s="312" t="inlineStr">
         <is>
           <t>후보 조회</t>
         </is>
       </c>
-      <c r="B6" s="304" t="inlineStr">
+      <c r="B6" s="312" t="inlineStr">
         <is>
           <t>/app/project-rooms/{roomId}/work</t>
         </is>
       </c>
-      <c r="C6" s="304" t="inlineStr">
+      <c r="C6" s="312" t="inlineStr">
         <is>
           <t>GET /api/project-rooms/{roomId}/agent/suggestions</t>
         </is>
       </c>
-      <c r="D6" s="304" t="inlineStr">
+      <c r="D6" s="312" t="inlineStr">
         <is>
           <t>연결</t>
         </is>
       </c>
-      <c r="E6" s="304" t="inlineStr">
+      <c r="E6" s="312" t="inlineStr">
         <is>
           <t>WBS/TASK/TODO 타입별로 후보 트레이 표시</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="304" t="inlineStr">
+      <c r="A7" s="312" t="inlineStr">
         <is>
           <t>후보 처리</t>
         </is>
       </c>
-      <c r="B7" s="304" t="inlineStr">
+      <c r="B7" s="312" t="inlineStr">
         <is>
           <t>/app/project-rooms/{roomId}/work</t>
         </is>
       </c>
-      <c r="C7" s="304" t="inlineStr">
+      <c r="C7" s="312" t="inlineStr">
         <is>
           <t>PATCH /api/agent/suggestions/{id}</t>
         </is>
       </c>
-      <c r="D7" s="304" t="inlineStr">
+      <c r="D7" s="312" t="inlineStr">
         <is>
           <t>연결</t>
         </is>
       </c>
-      <c r="E7" s="304" t="inlineStr">
+      <c r="E7" s="312" t="inlineStr">
         <is>
           <t>승인 시 작업판 다시 조회, 보류/제외 시 후보 목록 제거</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="304" t="inlineStr">
+      <c r="A8" s="312" t="inlineStr">
         <is>
           <t>WBS 기간 저장</t>
         </is>
       </c>
-      <c r="B8" s="304" t="inlineStr">
+      <c r="B8" s="312" t="inlineStr">
         <is>
           <t>/app/project-rooms/{roomId}/work</t>
         </is>
       </c>
-      <c r="C8" s="304" t="inlineStr">
+      <c r="C8" s="312" t="inlineStr">
         <is>
           <t>POST/PATCH /api/schedules</t>
         </is>
       </c>
-      <c r="D8" s="304" t="inlineStr">
+      <c r="D8" s="312" t="inlineStr">
         <is>
           <t>연결</t>
         </is>
       </c>
-      <c r="E8" s="304" t="inlineStr">
+      <c r="E8" s="312" t="inlineStr">
         <is>
           <t>간트 바 생성·이동·길이 조절이 일정 row와 연결</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="304" t="inlineStr">
-        <is>
-          <t>WBS 기간 초기화</t>
-        </is>
-      </c>
-      <c r="B9" s="304" t="inlineStr">
+      <c r="A9" s="312" t="inlineStr">
+        <is>
+          <t>WBS 기간 삭제</t>
+        </is>
+      </c>
+      <c r="B9" s="312" t="inlineStr">
         <is>
           <t>/app/project-rooms/{roomId}/work</t>
         </is>
       </c>
-      <c r="C9" s="304" t="inlineStr">
+      <c r="C9" s="312" t="inlineStr">
         <is>
           <t>DELETE /api/schedules/{scheduleId}</t>
         </is>
       </c>
-      <c r="D9" s="304" t="inlineStr">
+      <c r="D9" s="312" t="inlineStr">
         <is>
           <t>연결</t>
         </is>
       </c>
-      <c r="E9" s="304" t="inlineStr">
-        <is>
-          <t>서버 삭제 성공 후 화면 기간 제거. 실패 시 화면 유지</t>
+      <c r="E9" s="312" t="inlineStr">
+        <is>
+          <t>삭제/휴지통은 왼쪽 작업 목록에서만 제공. 간트 바는 이동·기간 조절만 담당</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="304" t="inlineStr">
+      <c r="A10" s="312" t="inlineStr">
         <is>
           <t>WBS 삭제</t>
         </is>
       </c>
-      <c r="B10" s="304" t="inlineStr">
+      <c r="B10" s="312" t="inlineStr">
         <is>
           <t>/app/project-rooms/{roomId}/work</t>
         </is>
       </c>
-      <c r="C10" s="304" t="inlineStr">
+      <c r="C10" s="312" t="inlineStr">
         <is>
           <t>DELETE /api/schedules/{scheduleId} -&gt; DELETE /api/wbs-items/{id}</t>
         </is>
       </c>
-      <c r="D10" s="304" t="inlineStr">
+      <c r="D10" s="312" t="inlineStr">
         <is>
           <t>연결</t>
         </is>
       </c>
-      <c r="E10" s="304" t="inlineStr">
+      <c r="E10" s="312" t="inlineStr">
         <is>
           <t>연결 일정 삭제 성공 후 WBS 삭제. 실패 시 화면과 DB를 둘 다 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="313" t="inlineStr">
+        <is>
+          <t>WBS 생성 UX</t>
+        </is>
+      </c>
+      <c r="B11" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C11" s="313" t="inlineStr">
+        <is>
+          <t>POST /api/project-rooms/{roomId}/wbs-items</t>
+        </is>
+      </c>
+      <c r="D11" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E11" s="313" t="inlineStr">
+        <is>
+          <t>상위 작업은 툴바에서 생성, 하위 작업은 선택한 줄 또는 왼쪽 줄 + 버튼에서만 생성. 타임라인 클릭 생성 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="313" t="inlineStr">
+        <is>
+          <t>간트 초기 스크롤</t>
+        </is>
+      </c>
+      <c r="B12" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C12" s="313" t="inlineStr">
+        <is>
+          <t>프론트 GanttProvider</t>
+        </is>
+      </c>
+      <c r="D12" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E12" s="313" t="inlineStr">
+        <is>
+          <t>처음 열 때 오늘 근처로 시작하고, 연도 확장 시 오른쪽 끝으로 자동 이동하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="313" t="inlineStr">
+        <is>
+          <t>Google Calendar 외부 삭제 반영</t>
+        </is>
+      </c>
+      <c r="B13" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work, /app/calendar</t>
+        </is>
+      </c>
+      <c r="C13" s="313" t="inlineStr">
+        <is>
+          <t>POST /api/calendar/sync</t>
+        </is>
+      </c>
+      <c r="D13" s="313" t="inlineStr">
+        <is>
+          <t>백엔드 수정</t>
+        </is>
+      </c>
+      <c r="E13" s="313" t="inlineStr">
+        <is>
+          <t>Google sync가 showDeleted=true로 cancelled 이벤트를 받고 같은 googleEventId 일정을 로컬 DB에서 제거</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7209,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="211" t="inlineStr">
         <is>
@@ -11607,7 +11709,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" s="154" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -2365,7 +2365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="D1" s="304" t="inlineStr">
         <is>
-          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화</t>
+          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화, WBS 스크롤/접힘 UX</t>
         </is>
       </c>
       <c r="E1" s="304" t="n"/>
@@ -2699,6 +2699,87 @@
       <c r="E13" s="313" t="inlineStr">
         <is>
           <t>Google sync가 showDeleted=true로 cancelled 이벤트를 받고 같은 googleEventId 일정을 로컬 DB에서 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="313" t="inlineStr">
+        <is>
+          <t>WBS 줄 클릭 동작</t>
+        </is>
+      </c>
+      <c r="B14" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C14" s="313" t="inlineStr">
+        <is>
+          <t>프론트 WBS Gantt</t>
+        </is>
+      </c>
+      <c r="D14" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E14" s="313" t="inlineStr">
+        <is>
+          <t>줄 클릭은 수정창을 열지 않고 해당 간트 바 위치로 이동. 수정은 연필 버튼으로 분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="313" t="inlineStr">
+        <is>
+          <t>WBS 하위 작업 접기</t>
+        </is>
+      </c>
+      <c r="B15" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C15" s="313" t="inlineStr">
+        <is>
+          <t>프론트 WBS Gantt</t>
+        </is>
+      </c>
+      <c r="D15" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E15" s="313" t="inlineStr">
+        <is>
+          <t>상위 줄에서 하위 작업을 접고 펼침. 접힌 하위 줄은 목록과 타임라인 바에서 함께 숨김</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="313" t="inlineStr">
+        <is>
+          <t>WBS 내부 스크롤 고정</t>
+        </is>
+      </c>
+      <c r="B16" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C16" s="313" t="inlineStr">
+        <is>
+          <t>프론트 GanttProvider</t>
+        </is>
+      </c>
+      <c r="D16" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E16" s="313" t="inlineStr">
+        <is>
+          <t>가로 스크롤 끝 도달 시 연도를 자동 확장하지 않음. 조작 중 오른쪽 끝으로 튀는 동작 제거</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 명세 맵핑" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드 카드 후보" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 용도·화면·위젯 맵" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작업판 후보·일정 삭제" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -155,8 +156,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002C3540"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -268,8 +273,18 @@
         <fgColor rgb="00EADCF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7EAF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border/>
     <border>
       <left style="thin">
@@ -545,11 +560,19 @@
         <color rgb="FFCDD8DF"/>
       </right>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1400,6 +1423,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2324,6 +2359,435 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="304" t="inlineStr">
+        <is>
+          <t>갱신일</t>
+        </is>
+      </c>
+      <c r="B1" s="304" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C1" s="304" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="D1" s="304" t="inlineStr">
+        <is>
+          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화, WBS 스크롤/접힘 UX</t>
+        </is>
+      </c>
+      <c r="E1" s="304" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="304" t="n"/>
+      <c r="B2" s="304" t="n"/>
+      <c r="C2" s="304" t="n"/>
+      <c r="D2" s="304" t="n"/>
+      <c r="E2" s="304" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="311" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="311" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="C3" s="311" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D3" s="311" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="E3" s="311" t="inlineStr">
+        <is>
+          <t>검증/규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="312" t="inlineStr">
+        <is>
+          <t>WBS 후보 생성</t>
+        </is>
+      </c>
+      <c r="B4" s="312" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C4" s="312" t="inlineStr">
+        <is>
+          <t>POST /api/ai/generate-wbs</t>
+        </is>
+      </c>
+      <c r="D4" s="312" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E4" s="312" t="inlineStr">
+        <is>
+          <t>버튼 클릭 후 DRAFT WBS 후보 재조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="312" t="inlineStr">
+        <is>
+          <t>칸반 후보 생성</t>
+        </is>
+      </c>
+      <c r="B5" s="312" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C5" s="312" t="inlineStr">
+        <is>
+          <t>POST /api/ai/generate-tasks</t>
+        </is>
+      </c>
+      <c r="D5" s="312" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E5" s="312" t="inlineStr">
+        <is>
+          <t>버튼 클릭 후 DRAFT TASK/TODO 후보 재조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="312" t="inlineStr">
+        <is>
+          <t>후보 조회</t>
+        </is>
+      </c>
+      <c r="B6" s="312" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C6" s="312" t="inlineStr">
+        <is>
+          <t>GET /api/project-rooms/{roomId}/agent/suggestions</t>
+        </is>
+      </c>
+      <c r="D6" s="312" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E6" s="312" t="inlineStr">
+        <is>
+          <t>WBS/TASK/TODO 타입별로 후보 트레이 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="312" t="inlineStr">
+        <is>
+          <t>후보 처리</t>
+        </is>
+      </c>
+      <c r="B7" s="312" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C7" s="312" t="inlineStr">
+        <is>
+          <t>PATCH /api/agent/suggestions/{id}</t>
+        </is>
+      </c>
+      <c r="D7" s="312" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E7" s="312" t="inlineStr">
+        <is>
+          <t>승인 시 작업판 다시 조회, 보류/제외 시 후보 목록 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="312" t="inlineStr">
+        <is>
+          <t>WBS 기간 저장</t>
+        </is>
+      </c>
+      <c r="B8" s="312" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C8" s="312" t="inlineStr">
+        <is>
+          <t>POST/PATCH /api/schedules</t>
+        </is>
+      </c>
+      <c r="D8" s="312" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E8" s="312" t="inlineStr">
+        <is>
+          <t>간트 바 생성·이동·길이 조절이 일정 row와 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="312" t="inlineStr">
+        <is>
+          <t>WBS 기간 삭제</t>
+        </is>
+      </c>
+      <c r="B9" s="312" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C9" s="312" t="inlineStr">
+        <is>
+          <t>DELETE /api/schedules/{scheduleId}</t>
+        </is>
+      </c>
+      <c r="D9" s="312" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E9" s="312" t="inlineStr">
+        <is>
+          <t>삭제/휴지통은 왼쪽 작업 목록에서만 제공. 간트 바는 이동·기간 조절만 담당</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="312" t="inlineStr">
+        <is>
+          <t>WBS 삭제</t>
+        </is>
+      </c>
+      <c r="B10" s="312" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C10" s="312" t="inlineStr">
+        <is>
+          <t>DELETE /api/schedules/{scheduleId} -&gt; DELETE /api/wbs-items/{id}</t>
+        </is>
+      </c>
+      <c r="D10" s="312" t="inlineStr">
+        <is>
+          <t>연결</t>
+        </is>
+      </c>
+      <c r="E10" s="312" t="inlineStr">
+        <is>
+          <t>연결 일정 삭제 성공 후 WBS 삭제. 실패 시 화면과 DB를 둘 다 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="313" t="inlineStr">
+        <is>
+          <t>WBS 생성 UX</t>
+        </is>
+      </c>
+      <c r="B11" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C11" s="313" t="inlineStr">
+        <is>
+          <t>POST /api/project-rooms/{roomId}/wbs-items</t>
+        </is>
+      </c>
+      <c r="D11" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E11" s="313" t="inlineStr">
+        <is>
+          <t>상위 작업은 툴바에서 생성, 하위 작업은 선택한 줄 또는 왼쪽 줄 + 버튼에서만 생성. 타임라인 클릭 생성 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="313" t="inlineStr">
+        <is>
+          <t>간트 초기 스크롤</t>
+        </is>
+      </c>
+      <c r="B12" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C12" s="313" t="inlineStr">
+        <is>
+          <t>프론트 GanttProvider</t>
+        </is>
+      </c>
+      <c r="D12" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E12" s="313" t="inlineStr">
+        <is>
+          <t>처음 열 때 오늘 근처로 시작하고, 연도 확장 시 오른쪽 끝으로 자동 이동하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="313" t="inlineStr">
+        <is>
+          <t>Google Calendar 외부 삭제 반영</t>
+        </is>
+      </c>
+      <c r="B13" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work, /app/calendar</t>
+        </is>
+      </c>
+      <c r="C13" s="313" t="inlineStr">
+        <is>
+          <t>POST /api/calendar/sync</t>
+        </is>
+      </c>
+      <c r="D13" s="313" t="inlineStr">
+        <is>
+          <t>백엔드 수정</t>
+        </is>
+      </c>
+      <c r="E13" s="313" t="inlineStr">
+        <is>
+          <t>Google sync가 showDeleted=true로 cancelled 이벤트를 받고 같은 googleEventId 일정을 로컬 DB에서 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="313" t="inlineStr">
+        <is>
+          <t>WBS 줄 클릭 동작</t>
+        </is>
+      </c>
+      <c r="B14" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C14" s="313" t="inlineStr">
+        <is>
+          <t>프론트 WBS Gantt</t>
+        </is>
+      </c>
+      <c r="D14" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E14" s="313" t="inlineStr">
+        <is>
+          <t>줄 클릭은 수정창을 열지 않고 해당 간트 바 위치로 이동. 수정은 연필 버튼으로 분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="313" t="inlineStr">
+        <is>
+          <t>WBS 하위 작업 접기</t>
+        </is>
+      </c>
+      <c r="B15" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C15" s="313" t="inlineStr">
+        <is>
+          <t>프론트 WBS Gantt</t>
+        </is>
+      </c>
+      <c r="D15" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E15" s="313" t="inlineStr">
+        <is>
+          <t>상위 줄에서 하위 작업을 접고 펼침. 접힌 하위 줄은 목록과 타임라인 바에서 함께 숨김</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="313" t="inlineStr">
+        <is>
+          <t>WBS 내부 스크롤 고정</t>
+        </is>
+      </c>
+      <c r="B16" s="313" t="inlineStr">
+        <is>
+          <t>/app/project-rooms/{roomId}/work</t>
+        </is>
+      </c>
+      <c r="C16" s="313" t="inlineStr">
+        <is>
+          <t>프론트 GanttProvider</t>
+        </is>
+      </c>
+      <c r="D16" s="313" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E16" s="313" t="inlineStr">
+        <is>
+          <t>가로 스크롤 끝 도달 시 연도를 자동 확장하지 않음. 조작 중 오른쪽 끝으로 튀는 동작 제거</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3031,12 +3495,12 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>wbsApi(+agent+projectRoom)</t>
+          <t>wbsApi+todoApi+calendarApi+agentApi</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>GET /wbs-board · /wbs-items · POST /wbs-items · PATCH /wbs-items/{id} · DELETE /wbs-items/{id} · reorder</t>
+          <t>GET /wbs-board · /wbs-items · POST/PATCH/DELETE /wbs-items · POST/PATCH/DELETE /api/schedules · POST /api/ai/generate-wbs · POST /api/ai/generate-tasks · GET /project-rooms/{id}/agent/suggestions · PATCH /agent/suggestions/{id}</t>
         </is>
       </c>
       <c r="F14" s="64" t="inlineStr">
@@ -3071,7 +3535,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-01 실제 로컬 백엔드 데이터(WBS 10·TODO 6)와 Playwright 캡처로 확인. 칸반 카드 제목·상태칩·보조문구 폰트 밀도 조정.</t>
+          <t>WBS/칸반/후보를 탭 전환으로 분리. WBS는 Jira식 줄 목록+우측 상세, 하위 WBS 색 라인/색상 선택, 월·주·일 기간 보기로 정리. 칸반은 가로 4열 드래그 보드 유지. 2026-07-03 WBS 후보 생성은 agentApi.generateWbs, 칸반 후보 생성은 agentApi.generateTasks에 연결. 후보 목록/승인·보류·제외는 /api/project-rooms/{roomId}/agent/suggestions와 /api/agent/suggestions/{id} 사용. WBS 기간 생성/수정/초기화/삭제는 /api/schedules를 사용하고, 삭제는 백엔드의 Google Calendar 동기화 삭제와 DB 삭제 성공 후 화면에서 제거.</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3928,7 @@
       </c>
       <c r="I22" s="64" t="inlineStr">
         <is>
-          <t>부분(후보 생성 실데이터 필요)</t>
+          <t>부분(실계정 검증 필요)</t>
         </is>
       </c>
       <c r="J22" s="24" t="inlineStr">
@@ -3479,7 +3943,7 @@
       </c>
       <c r="L22" s="25" t="inlineStr">
         <is>
-          <t>최신 백엔드 #143-#145 API 래퍼 추가. 화면은 기존 후보함 중심, 생성문서/확정요구사항은 API어댑터 준비.</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에서 WBS 후보 생성 버튼은 agentApi.generateWbs, 칸반 후보 생성 버튼은 agentApi.generateTasks에 연결. DRAFT 후보 목록을 불러오고 승인·보류·제외를 PATCH /api/agent/suggestions/{id}로 처리.</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4745,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -6667,7 +7130,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>
@@ -7240,7 +7702,7 @@
       </c>
       <c r="F21" s="215" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+작업판 버튼</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7730,7 @@
       </c>
       <c r="F22" s="215" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+작업판 버튼</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10930,7 @@
       </c>
       <c r="F154" s="216" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12594,7 @@
       </c>
       <c r="J8" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 후보 트레이에서 DRAFT 후보 조회와 승인·보류·제외 액션으로 사용.</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12646,7 @@
       </c>
       <c r="J9" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 후보 트레이에서 DRAFT 후보 조회와 승인·보류·제외 액션으로 사용.</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12896,7 @@
       </c>
       <c r="H14" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+화면연결</t>
         </is>
       </c>
       <c r="I14" s="304" t="inlineStr">
@@ -12444,7 +12906,7 @@
       </c>
       <c r="J14" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에 WBS 후보 생성, 칸반 후보 생성 버튼 연결. 생성 후 DRAFT 후보 목록을 다시 조회.</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12948,7 @@
       </c>
       <c r="H15" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API어댑터+화면연결</t>
         </is>
       </c>
       <c r="I15" s="304" t="inlineStr">
@@ -12496,7 +12958,7 @@
       </c>
       <c r="J15" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 /app/project-rooms/{roomId}/work에 WBS 후보 생성, 칸반 후보 생성 버튼 연결. 생성 후 DRAFT 후보 목록을 다시 조회.</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16546,7 @@
       </c>
       <c r="J84" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>작업판 후보 트레이에서 DRAFT 후보 조회와 승인·보류·제외 액션으로 사용.</t>
         </is>
       </c>
     </row>
@@ -18092,7 +18554,7 @@
       </c>
       <c r="F123" s="304" t="inlineStr">
         <is>
-          <t>/app/calendar, /app/project-rooms/{roomId}, 일정 버블</t>
+          <t>/app/calendar, /app/project-rooms/{roomId}/work, 일정 버블</t>
         </is>
       </c>
       <c r="G123" s="304" t="inlineStr">
@@ -18112,7 +18574,7 @@
       </c>
       <c r="J123" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>WBS 기간 바 생성·이동·길이 조절에서 일정 row를 생성/수정해 Google Calendar 동기화 기준으로 사용.</t>
         </is>
       </c>
     </row>
@@ -18144,7 +18606,7 @@
       </c>
       <c r="F124" s="304" t="inlineStr">
         <is>
-          <t>/app/calendar, /app/project-rooms/{roomId}, 일정 버블</t>
+          <t>/app/calendar, /app/project-rooms/{roomId}/work, 일정 버블</t>
         </is>
       </c>
       <c r="G124" s="304" t="inlineStr">
@@ -18154,7 +18616,7 @@
       </c>
       <c r="H124" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
       <c r="I124" s="304" t="inlineStr">
@@ -18164,7 +18626,7 @@
       </c>
       <c r="J124" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 WBS 기간 초기화와 WBS 삭제에서 /api/schedules/{scheduleId}를 먼저 호출. 백엔드가 Google Calendar 이벤트와 DB row를 지우며, 성공 후 화면에서 제거.</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18658,7 @@
       </c>
       <c r="F125" s="304" t="inlineStr">
         <is>
-          <t>/app/calendar, /app/project-rooms/{roomId}, 일정 버블</t>
+          <t>/app/calendar, /app/project-rooms/{roomId}/work, 일정 버블</t>
         </is>
       </c>
       <c r="G125" s="304" t="inlineStr">
@@ -18206,7 +18668,7 @@
       </c>
       <c r="H125" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결</t>
         </is>
       </c>
       <c r="I125" s="304" t="inlineStr">
@@ -18216,7 +18678,7 @@
       </c>
       <c r="J125" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>WBS 기간 바 생성·이동·길이 조절에서 일정 row를 생성/수정해 Google Calendar 동기화 기준으로 사용.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1764,7 +1764,7 @@
     <row r="2">
       <c r="A2" s="193" t="inlineStr">
         <is>
-          <t>측정 기준: 기능/API CSV·색상표, 최신 백엔드 origin/develop 03f7541, 프론트 코드 실측 · 헤드라인=① 가중합</t>
+          <t>측정 기준: 기능/API CSV·색상표, 최신 프론트 origin/develop 4505a60, 프론트 코드+Windows Tauri dev 실측 · 헤드라인=① 가중합</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C13" s="203" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="D13" s="285" t="inlineStr">
         <is>
-          <t>타우리 6기능 평균(위젯창65·SQLite76·폴더74·앱감지58·아웃박스58·사용량62)</t>
+          <t>타우리 6기능 평균(위젯창88·SQLite76·폴더74·앱감지58·아웃박스58·사용량62), 위젯 런타임은 Windows tauri:dev 25초 관찰까지 완료</t>
         </is>
       </c>
       <c r="E13" s="232" t="n"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D14" s="285" t="inlineStr">
         <is>
-          <t>typecheck 통과 · tauri/product/diff 재검증 예정 · 최신 API 경로 정정</t>
+          <t>typecheck/product-rules/tauri-boundaries/cargo check/cargo test 통과 · Tauri widget hydration/event 권한 로그 재검증</t>
         </is>
       </c>
       <c r="E14" s="232" t="n"/>
@@ -5710,17 +5710,17 @@
       </c>
       <c r="B4" s="89" t="inlineStr">
         <is>
-          <t>O · lib.rs 26개 invoke_handler + close destroy + exit cleanup</t>
+          <t>O · lib.rs 26개 invoke_handler + 투명/무테 창 + async widget build + cleanup</t>
         </is>
       </c>
       <c r="C4" s="78" t="inlineStr">
         <is>
-          <t>활성(26개 command, local 14개 active 승격)</t>
+          <t>활성(/api/widget/settings 기반 enabled 위젯 자동 실행 + 중복 실행 guard)</t>
         </is>
       </c>
       <c r="D4" s="99" t="inlineStr">
         <is>
-          <t>O · 위젯 화면</t>
+          <t>O · 로그인 후 하이브리드 앱+데스크탑 위젯</t>
         </is>
       </c>
       <c r="E4" s="99" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F4" s="80" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="G4" s="80" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H4" s="89" t="inlineStr">
         <is>
-          <t>후속(2026-07-01): close_widget_window는 WebViewWindow.destroy()로 해제. 최소화/토글 숨김은 WebView 유지. 앱 종료 시 bubli-widget-* 정리. 실제 tauri:dev 창 검증은 남음.</t>
+          <t>2026-07-03 Tauri 위젯 런타임 보강: 로그인 세션 복원 이벤트 중복 emit 차단, app_ready 중복 오픈 제거, 이미 열린 위젯의 focus/position 반복 적용 차단, enabled 위젯 startup guard 추가. desktop-widget SSR hydration mismatch와 core:event capability 누락을 수정했고, transparent html/body surface + 컴포넌트 전용 그림자 여백으로 사각 배경/스크롤바 노출을 줄임. 검증: npm run typecheck, npm run check:product-rules, npm run check:tauri-boundaries, cargo check, cargo test(29), tauri:dev 25초 관찰(위젯 hydration/event 권한 에러 재발 없음, 프로세스 폭증 없음). 남은 범위: 각 위젯 세부 기능의 장시간 실사용 QA와 로컬 파일/활동 감지 전체 플로우 검증.</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       <c r="E11" s="97" t="inlineStr"/>
       <c r="F11" s="81" t="inlineStr">
         <is>
-          <t>~69%</t>
+          <t>~72%</t>
         </is>
       </c>
       <c r="G11" s="81" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H11" s="97" t="inlineStr">
         <is>
-          <t>로컬 command 14개 active 승격 + 위젯 close/exit cleanup 적용. 남은 건 Windows 앱감지·native watch 런타임·실제 Tauri 창 검증.</t>
+          <t>위젯 런타임은 Windows tauri:dev에서 중복 오픈/깜빡임/권한 로그를 재검증. 남은 큰 축은 Windows 앱감지, 네이티브 폴더 watch 장시간 QA, 로컬 파일/활동 감지의 실사용 데이터 왕복 검증.</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B12" s="221" t="inlineStr">
         <is>
-          <t>단기 수정 적용: close_widget_window hide→destroy, 앱 종료 시 bubli-widget-* destroy cleanup. 현재 QA 자동 시작 경로는 전체 8개 버블 창을 동시에 열지 않음. 상세: docs/troubleshooting/위젯_메모리_런타임_분석_2026-07-01.md</t>
+          <t>2026-07-03: 위젯 연속 재오픈/물결식 재배치 원인을 세션 복원 이벤트 루프 + app_ready 중복 오픈 + 기존 창 focus/position 재적용으로 보고 차단. capability default 추가로 widget event.listen 권한 오류 제거.</t>
         </is>
       </c>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="H144" s="306" t="inlineStr">
         <is>
-          <t>화면연결</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I144" s="304" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="J144" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="H145" s="306" t="inlineStr">
         <is>
-          <t>화면연결</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I145" s="304" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="J145" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>
@@ -19760,7 +19760,7 @@
       </c>
       <c r="H146" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I146" s="304" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="J146" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="H147" s="306" t="inlineStr">
         <is>
-          <t>화면연결</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I147" s="304" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="J147" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="H148" s="306" t="inlineStr">
         <is>
-          <t>화면연결</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I148" s="304" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="J148" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="H149" s="306" t="inlineStr">
         <is>
-          <t>화면연결</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I149" s="304" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="J149" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="H150" s="306" t="inlineStr">
         <is>
-          <t>화면연결</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I150" s="304" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="J150" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="H151" s="306" t="inlineStr">
         <is>
-          <t>화면연결</t>
+          <t>화면연결+런타임검증</t>
         </is>
       </c>
       <c r="I151" s="304" t="inlineStr">
@@ -20030,7 +20030,7 @@
       </c>
       <c r="J151" s="304" t="inlineStr">
         <is>
-          <t>현재 화면에서 실제 API 우선 사용</t>
+          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D14" s="285" t="inlineStr">
         <is>
-          <t>typecheck/product-rules/tauri-boundaries/cargo check/cargo test 통과 · Tauri widget hydration/event 권한 로그 재검증</t>
+          <t>typecheck/lint/product-rules/tauri-boundaries/cargo fmt/check ?? ? ?? ?? ?? ?? ?? ? ?? show ?? ??</t>
         </is>
       </c>
       <c r="E14" s="232" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C4" s="78" t="inlineStr">
         <is>
-          <t>활성(/api/widget/settings 기반 enabled 위젯 자동 실행 + 중복 실행 guard)</t>
+          <t>??(bar+TODO ?? ??, ??? ??? ??? ??/??)</t>
         </is>
       </c>
       <c r="D4" s="99" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F4" s="80" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G4" s="80" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H4" s="89" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 위젯 런타임 보강: 로그인 세션 복원 이벤트 중복 emit 차단, app_ready 중복 오픈 제거, 이미 열린 위젯의 focus/position 반복 적용 차단, enabled 위젯 startup guard 추가. desktop-widget SSR hydration mismatch와 core:event capability 누락을 수정했고, transparent html/body surface + 컴포넌트 전용 그림자 여백으로 사각 배경/스크롤바 노출을 줄임. 검증: npm run typecheck, npm run check:product-rules, npm run check:tauri-boundaries, cargo check, cargo test(29), tauri:dev 25초 관찰(위젯 hydration/event 권한 에러 재발 없음, 프로세스 폭증 없음). 남은 범위: 각 위젯 세부 기능의 장시간 실사용 QA와 로컬 파일/활동 감지 전체 플로우 검증.</t>
+          <t>2026-07-03 Tauri ?? ??? ?? ??: ??? ? ???? ????/????/??? ???? ?? ????, ???? bar+TODO ?? ??? ?? ?? ??? 120ms ???? ???? ???? ??? ??. ?? ?? ??? ?? show()? ???? ?? ?? ??? ?? ??? ?? ?? ??? ??. desktop-widget mounted ??? useSyncExternalStore? ?? CI lint ?? ??. ??: npm run lint(?? ???), npm run typecheck, npm run check:product-rules, npm run check:tauri-boundaries, cargo fmt --check, cargo check ??. ?? ??: ?? ??? ???? ??? ?? ??/?? QA.</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B12" s="221" t="inlineStr">
         <is>
-          <t>2026-07-03: 위젯 연속 재오픈/물결식 재배치 원인을 세션 복원 이벤트 루프 + app_ready 중복 오픈 + 기존 창 focus/position 재적용으로 보고 차단. capability default 추가로 widget event.listen 권한 오류 제거.</t>
+          <t>2026-07-03: ?? ?? ???/??? ??? ??? ??? ? ?? ?? ??? ?? + ?? ? ?? show? ??. ??? ?? ??? bar+TODO? ????, ?? ??? ??? show()? ????? ??? ??. capability default ??? widget event.listen ?? ??? ???.</t>
         </is>
       </c>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="H144" s="306" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I144" s="304" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="J144" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="H145" s="306" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I145" s="304" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="J145" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -19760,7 +19760,7 @@
       </c>
       <c r="H146" s="305" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I146" s="304" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="J146" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="H147" s="306" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I147" s="304" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="J147" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="H148" s="306" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I148" s="304" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="J148" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="H149" s="306" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I149" s="304" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="J149" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="H150" s="306" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I150" s="304" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="J150" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="H151" s="306" t="inlineStr">
         <is>
-          <t>화면연결+런타임검증</t>
+          <t>????+??????</t>
         </is>
       </c>
       <c r="I151" s="304" t="inlineStr">
@@ -20030,7 +20030,7 @@
       </c>
       <c r="J151" s="304" t="inlineStr">
         <is>
-          <t>2026-07-03 Tauri 로그인 후 /api/widget/settings 기반 enabled 위젯 자동 실행, /desktop-widget hydration 안정화, core:event capability 추가, 중복 오픈/재배치 루프 차단. 세부 위젯별 장시간 기능 QA는 후속.</t>
+          <t>2026-07-03 Tauri ??? ? ?? ???? ??/??/??? ???? ?? ??. ?? ?? ??? bar+TODO ?? ???? ????, ??? ??? ??? ??/?? ???? ??? ?? ?? ?? ??/??? ?? ??. ?? ??? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D14" s="285" t="inlineStr">
         <is>
-          <t>typecheck/lint/product-rules/tauri-boundaries/cargo fmt/check ?? ? ?? ?? ?? ?? ?? ? ?? show ?? ??</t>
+          <t>typecheck/lint/product-rules/tauri-boundaries/cargo fmt/check/test ?? ? ?? ?? ?? ??? + ?? ?? ??? ??? DTO ??? ??</t>
         </is>
       </c>
       <c r="E14" s="232" t="n"/>
@@ -15127,12 +15127,12 @@
       </c>
       <c r="G57" s="304" t="inlineStr">
         <is>
-          <t>managedFolderApi + Tauri local clients</t>
+          <t>managedFolderApi + Tauri local clients + watch event listener</t>
         </is>
       </c>
       <c r="H57" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API???+???????</t>
         </is>
       </c>
       <c r="I57" s="304" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="J57" s="304" t="inlineStr">
         <is>
-          <t>Tauri 로컬 폴더 승인 이벤트만 서버로 동기화. 로컬 파일 탐색은 IPC 책임</t>
+          <t>2026-07-03 localEventId ?? payload ??? ??, Tauri watch ???? auto-sync ?? ??. ?? ??? ?? QA? ??.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D14" s="285" t="inlineStr">
         <is>
-          <t>typecheck/lint/product-rules/tauri-boundaries/cargo fmt/check/test ?? ? ?? ?? ?? ??? + ?? ?? ??? ??? DTO ??? ??</t>
+          <t>typecheck/lint/product-rules/tauri-boundaries/cargo fmt/check/test ?? ? ??/?? ??/?? ??? ??? ??? ??</t>
         </is>
       </c>
       <c r="E14" s="232" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="H3" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API???+???????</t>
         </is>
       </c>
       <c r="I3" s="304" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="J3" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 ?? POST ??? today ?? ??? ??? local_activity_buffer ?? ??? ?? ??. ?? ???/?? ??? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="H4" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API???+???????</t>
         </is>
       </c>
       <c r="I4" s="304" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="J4" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 ?? POST ??? today ?? ??? ??? local_activity_buffer ?? ??? ?? ??. ?? ???/?? ??? QA? ??.</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="H5" s="305" t="inlineStr">
         <is>
-          <t>API어댑터</t>
+          <t>API???+???????</t>
         </is>
       </c>
       <c r="I5" s="304" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="J5" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>2026-07-03 ?? POST ??? today ?? ??? ??? local_activity_buffer ?? ??? ?? ??. ?? ???/?? ??? QA? ??.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -3469,7 +3469,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보 보기 전환 유지. WBS는 Jira식 행 기반 간트로 정리하고, 상위 작업/하위 작업 관계를 왼쪽 목록에서 바로 보이게 함. 상위 행의 +는 하위 작업 생성, 하위 행의 +는 같은 상위 아래 형제 작업 생성으로 정리. 간트 바는 편집 버튼 없이 기간 이동/길이 조정만 담당. 칸반은 연결 WBS와 담당자 표시를 유지. 2026-07-02 PR #129에서 typecheck/build/visual-qa 통과, 리뷰 대기.</t>
+          <t>WBS/칸반/후보 보기 전환 유지. WBS는 Jira식 행 기반 간트로 정리하고, 상위 작업/하위 작업 관계를 왼쪽 목록에서 바로 보이게 함. 상위 작업 추가는 최상위 줄을 만들고, 선택 줄 하위 추가와 각 행의 +는 선택한 줄 바로 아래 하위 작업을 만든다. 간트 바는 편집 버튼 없이 기간 이동/길이 조정만 담당. 칸반은 연결 WBS와 담당자 표시를 유지. 2026-07-03 PR #133에서 WBS 생성 이름 선입력, 칸반 WBS/담당자 연결, 드래그 중 스크롤 좌표 안정화 보강.</t>
         </is>
       </c>
     </row>
@@ -5610,6 +5610,13 @@
           <t>타우리 데스크탑 앱 · 로컬 기능 (프론트 담당) · 2026-07-03 (코덱스 메모리수정 반영)</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="232" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="285" t="inlineStr">
@@ -5617,6 +5624,13 @@
           <t>어댑터 14개 command 전부 완비(브라우저=데스크탑앱 안내 분기). 로컬 14개 active 승격. 위젯 close→destroy·앱 종료 cleanup 적용. 실제 tauri:dev 창 검증만 남음.</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="232" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="338" t="inlineStr">
@@ -5991,6 +6005,12 @@
           <t>단기 수정 적용: close hide→destroy, 앱 종료 시 bubli-widget-* destroy. QA 자동시작은 8버블 동시 오픈 안 함. 중장기 경량 위젯 런타임 분리는 후속. 상세: docs/troubleshooting/위젯_메모리_런타임_분석_2026-07-01.md</t>
         </is>
       </c>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="232" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="350" t="inlineStr">
@@ -6010,6 +6030,8 @@
           <t>JS 활성+화면 연결·검증</t>
         </is>
       </c>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="232" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="348" t="inlineStr">
@@ -6022,6 +6044,8 @@
           <t>일부·검증 남음</t>
         </is>
       </c>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="232" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="351" t="inlineStr">
@@ -6034,6 +6058,8 @@
           <t>미연결</t>
         </is>
       </c>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="232" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6574,7 +6600,7 @@
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보 보기 전환 유지. WBS는 상위/하위 행 관계를 목록에서 조작하고, 간트 바는 날짜 위치와 기간 조정만 처리. 하위 작업 생성은 부모 WBS 행의 +에서 시작되며 같은 부모 아래 형제 추가도 지원. 2026-07-02 PR #129 build/visual-qa 통과.</t>
+          <t>WBS/칸반/후보 보기 전환 유지. WBS는 상위/하위 행 관계를 목록에서 조작하고, 간트 바는 날짜 위치와 기간 조정만 처리. 하위 작업 생성은 선택한 WBS 행의 + 또는 선택 줄 하위 추가에서 시작되며, 선택 줄 바로 아래 parentId로 생성되도록 보강. 2026-07-03 PR #133 build/visual-qa 통과 후 추가 UX 안정화 진행.</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17785,7 @@
       </c>
       <c r="J103" s="304" t="inlineStr">
         <is>
-          <t>작업판 WBS 행 목록, 상위/하위 연결, 하위 색 라인, 월/주/일 기간 보기, 칸반 전환 기준 유지. 상위/하위 생성은 왼쪽 WBS 목록 액션으로 정리하고 간트 바는 기간 조정만 담당. 2026-07-02 PR #129 CI 통과.</t>
+          <t>작업판 WBS 행 목록, 상위/하위 연결, 하위 색 라인, 월/주/일 기간 보기, 칸반 전환 기준 유지. 상위/하위 생성은 왼쪽 WBS 목록 액션으로 정리하고 간트 바는 기간 조정만 담당. 2026-07-03 선택 줄 하위 생성 parentId 기준과 드래그 중 스크롤 좌표 안정화 보강.</t>
         </is>
       </c>
     </row>
@@ -17863,7 +17889,7 @@
       </c>
       <c r="J105" s="304" t="inlineStr">
         <is>
-          <t>WBS 생성은 상위 작업 추가와 부모 행 기준 하위 작업 추가를 구분. parentId 기반 생성 UI를 왼쪽 WBS 목록 액션에 연결.</t>
+          <t>WBS 생성은 상위 작업 추가와 선택 줄 하위 작업 추가를 구분. parentId 기반 생성 UI를 왼쪽 WBS 목록 액션에 연결했고, 각 행의 +는 해당 행 바로 아래 하위 작업을 생성하도록 정리.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -3469,7 +3469,7 @@
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보 보기 전환 유지. WBS는 Jira식 행 기반 간트로 정리하고, 상위 작업/하위 작업 관계를 왼쪽 목록에서 바로 보이게 함. 상위 작업 추가는 최상위 줄을 만들고, 선택 줄 하위 추가와 각 행의 +는 선택한 줄 바로 아래 하위 작업을 만든다. 간트 바는 편집 버튼 없이 기간 이동/길이 조정만 담당. 칸반은 연결 WBS와 담당자 표시를 유지. 2026-07-03 PR #133에서 WBS 생성 이름 선입력, 칸반 WBS/담당자 연결, 드래그 중 스크롤 좌표 안정화 보강.</t>
+          <t>WBS/칸반/후보 보기 전환 유지. WBS는 Jira식 행 기반 간트로 정리하고, 상위 작업/하위 작업 관계를 왼쪽 목록에서 바로 보이게 함. 상위 작업 추가는 최상위 줄을 만들고, 선택 줄 하위 추가와 각 행의 +는 선택한 줄 바로 아래 하위 작업을 만든다. 간트 바는 편집 버튼 없이 기간 이동/길이 조정만 담당. 칸반은 연결 WBS와 담당자 표시를 유지. 2026-07-03 PR #133에서 WBS 생성 이름 선입력, 칸반 WBS/담당자 연결, 드래그 중 스크롤 좌표 안정화 보강. 칸반 담당자 선택은 프로젝트룸 멤버의 avatarUrl을 실제 이미지로 렌더링하도록 보강.</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보 보기 전환 유지. WBS는 상위/하위 행 관계를 목록에서 조작하고, 간트 바는 날짜 위치와 기간 조정만 처리. 하위 작업 생성은 선택한 WBS 행의 + 또는 선택 줄 하위 추가에서 시작되며, 선택 줄 바로 아래 parentId로 생성되도록 보강. 2026-07-03 PR #133 build/visual-qa 통과 후 추가 UX 안정화 진행.</t>
+          <t>WBS/칸반/후보 보기 전환 유지. WBS는 상위/하위 행 관계를 목록에서 조작하고, 간트 바는 날짜 위치와 기간 조정만 처리. 하위 작업 생성은 선택한 WBS 행의 + 또는 선택 줄 하위 추가에서 시작되며, 선택 줄 바로 아래 parentId로 생성되도록 보강. 2026-07-03 PR #133 build/visual-qa 통과 후 추가 UX 안정화 진행. 칸반 담당자 메뉴는 멤버 API의 avatarUrl과 현재 로그인 사용자 프로필 보강값을 사용.</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="J130" s="304" t="inlineStr">
         <is>
-          <t>칸반 드래그/상태 버튼에서 PATCH /api/tasks/{taskId} 호출. 화면 검증 완료</t>
+          <t>칸반 드래그/상태 버튼에서 PATCH /api/tasks/{taskId} 호출. 화면 검증 완료 담당자 변경 UI에서 프로젝트룸 멤버 프로필 이미지 표시 보강.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -3221,7 +3221,8 @@
       </c>
       <c r="L10" s="25" t="inlineStr">
         <is>
-          <t>다른 룸 화면 진입점</t>
+          <t>다른 룸 화면 진입점
+WBS 간트는 첫 진입 시 오늘 기준 구간으로 맞추고, 좌측 작업 목록 고정과 하위 작업 색 라인을 보강.</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6559,8 @@
       </c>
       <c r="H12" s="97" t="inlineStr">
         <is>
-          <t>목록/업로드 API 우선. 업로드 실패 시 목업 파일 성공 처리 제거. 댓글·버전·요약은 API어댑터 준비.</t>
+          <t>목록/업로드 API 우선. 업로드 실패 시 목업 파일 성공 처리 제거. 댓글·버전·요약은 API어댑터 준비.
+프로젝트룸 작업판 WBS는 오늘 기준 표시/좌측 목록 고정/하위 작업 구분을 보강. Google 다른 캘린더 분리는 회의 후 백엔드 scope·calendarId 저장 설계 필요.</t>
         </is>
       </c>
     </row>
@@ -19085,7 +19087,8 @@
       </c>
       <c r="J128" s="304" t="inlineStr">
         <is>
-          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속</t>
+          <t>프론트 래퍼는 준비됐고 화면 소비/실계정 검증은 후속
+WBS 간트 표시 안정화: 초기 오늘 위치, 드래그 중 자동 스크롤 억제 흐름 유지, 하위 작업 색상 구분 보강.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -6602,7 +6602,7 @@
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>WBS/칸반/후보 보기 전환 유지. WBS는 상위/하위 행 관계를 목록에서 조작하고, 간트 바는 날짜 위치와 기간 조정만 처리. 하위 작업 생성은 선택한 WBS 행의 + 또는 선택 줄 하위 추가에서 시작되며, 선택 줄 바로 아래 parentId로 생성되도록 보강. 2026-07-03 PR #133 build/visual-qa 통과 후 추가 UX 안정화 진행. 칸반 담당자 메뉴는 멤버 API의 avatarUrl과 현재 로그인 사용자 프로필 보강값을 사용.</t>
+          <t>WBS/칸반/후보 보기 전환 유지. WBS는 상위/하위 행 관계를 목록에서 조작하고, 간트 바는 날짜 위치와 기간 조정만 처리. 하위 작업 생성은 선택한 WBS 행의 + 또는 선택 줄 하위 추가에서 시작되며, 선택 줄 바로 아래 parentId로 생성되도록 보강. 2026-07-03 PR #133 build/visual-qa 통과 후 추가 UX 안정화 진행. 칸반 담당자 메뉴는 멤버 API의 avatarUrl과 현재 로그인 사용자 프로필 보강값을 사용. / 2026-07-03 #133: 칸반 카드에서 연결된 WBS를 부모/하위 경로로 표시하고, 담당자는 실제 멤버 프로필 이미지와 함께 선택/변경 가능하게 보강.</t>
         </is>
       </c>
     </row>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="J130" s="304" t="inlineStr">
         <is>
-          <t>칸반 드래그/상태 버튼에서 PATCH /api/tasks/{taskId} 호출. 화면 검증 완료 담당자 변경 UI에서 프로젝트룸 멤버 프로필 이미지 표시 보강.</t>
+          <t>칸반 드래그/상태 버튼에서 PATCH /api/tasks/{taskId} 호출. 화면 검증 완료 담당자 변경 UI에서 프로젝트룸 멤버 프로필 이미지 표시 보강. / 2026-07-03 #133: /api/tasks/{taskId} PATCH 흐름에 WBS 연결 변경과 담당자 변경 UI가 붙었고, 카드에는 WBS 경로가 표시됨.</t>
         </is>
       </c>
     </row>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1768,6 +1768,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1798,6 +1799,7 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1993,6 +1995,7 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -2027,6 +2030,7 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2098,6 +2102,7 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2185,6 +2190,7 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2229,7 +2235,7 @@
       </c>
       <c r="D34" s="285" t="inlineStr">
         <is>
-          <t>일정 재정비(모바일 미확인)·자료보드 재작업 중</t>
+          <t>일정 재정비·자료보드 빈 상태 정리 반영(실파일 업로드·모바일/앱 런타임 검증 남음)</t>
         </is>
       </c>
       <c r="E34" s="232" t="n"/>
@@ -2272,6 +2278,7 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -3473,7 +3480,7 @@
       </c>
       <c r="L13" s="25" t="inlineStr">
         <is>
-          <t>룸 자료 목록/업로드 API 우선. 업로드 실패 시 preview 리소스 성공 처리 제거.</t>
+          <t>룸 자료 목록/업로드 API 우선. 업로드 실패 성공 처리 제거. 2026-07-03 빈 상태를 카드형 파일처럼 보이지 않도록 중앙 안내로 정리하고, 선택/드래그 업로드 경계를 유지.</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3684,7 @@
       </c>
       <c r="L17" s="25" t="inlineStr">
         <is>
-          <t>개인 자료는 서버 목록 API와 Tauri 로컬 폴더 경계로 분리. /api/me/managed-folders, /api/local-files 등 미구현 서버 경로 제거.</t>
+          <t>개인 자료는 서버 목록 API와 Tauri 로컬 폴더 경계로 분리. 브라우저는 로컬 폴더 연결 안내만 표시하고, 빈 상태를 중앙 안내로 정리.</t>
         </is>
       </c>
     </row>
@@ -4745,6 +4752,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -6575,12 +6583,12 @@
       </c>
       <c r="G12" s="216" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>개선 반영</t>
         </is>
       </c>
       <c r="H12" s="97" t="inlineStr">
         <is>
-          <t>목록/업로드 API 우선. 업로드 실패 시 목업 파일 성공 처리 제거. 댓글·버전·요약은 API어댑터 준비.</t>
+          <t>목록/업로드 API 우선. 업로드 실패 성공 처리 제거. 빈 자료 상태는 파일 카드가 아니라 중앙 안내 문구로 정리. 댓글·버전·요약은 API어댑터 준비.</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6709,12 @@
       </c>
       <c r="G15" s="216" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>개선 반영</t>
         </is>
       </c>
       <c r="H15" s="97" t="inlineStr">
         <is>
-          <t>개인 자료는 서버 목록 API와 Tauri 로컬 폴더 경계로 분리. 미구현 서버 관리폴더 API 제거.</t>
+          <t>개인 자료는 서버 목록 API와 Tauri 로컬 폴더 경계로 분리. 브라우저 안내 문구를 로컬 폴더 연결 기준으로 정리하고 빈 상태 카드형 UI 제거.</t>
         </is>
       </c>
     </row>
@@ -7130,6 +7138,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1768,7 +1768,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1799,7 +1798,6 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1995,7 +1993,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -2030,7 +2027,6 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2102,7 +2098,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2190,7 +2185,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2278,7 +2272,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -3134,7 +3127,7 @@
       </c>
       <c r="L6" s="25" t="inlineStr">
         <is>
-          <t>세션 refresh·logout 연결</t>
+          <t>세션 refresh·logout 연결. 2026-07-03 작은 창 배경 끊김 Playwright 확인.</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4745,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -6331,12 +6323,12 @@
       </c>
       <c r="G6" s="216" t="inlineStr">
         <is>
-          <t>부분</t>
+          <t>Playwright 확인</t>
         </is>
       </c>
       <c r="H6" s="89" t="inlineStr">
         <is>
-          <t>디자인 완료 · 반응형 미확인</t>
+          <t>디자인 완료 · 2026-07-03 로그인 배경 끊김 방지. 674x610·674x900·448x563 Playwright 캡처에서 main 높이/배경/콘솔 에러 0 확인. OAuth 호환 라우트는 기존 흐름 유지.</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7130,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -1768,7 +1768,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="279" t="inlineStr">
         <is>
@@ -1799,7 +1798,6 @@
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="232" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="283" t="inlineStr">
         <is>
@@ -1995,7 +1993,6 @@
       </c>
       <c r="E15" s="232" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="283" t="inlineStr">
         <is>
@@ -2030,7 +2027,6 @@
       </c>
       <c r="E18" s="232" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="283" t="inlineStr">
         <is>
@@ -2102,7 +2098,6 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="232" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="283" t="inlineStr">
         <is>
@@ -2190,7 +2185,6 @@
       </c>
       <c r="E30" s="232" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="283" t="inlineStr">
         <is>
@@ -2278,7 +2272,6 @@
       </c>
       <c r="E36" s="232" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="283" t="inlineStr">
         <is>
@@ -2400,7 +2393,7 @@
       </c>
       <c r="D1" s="304" t="inlineStr">
         <is>
-          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화, WBS 스크롤/접힘 UX</t>
+          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화, WBS 스크롤/접힘 UX, 드래그 스크롤 안정화</t>
         </is>
       </c>
       <c r="E1" s="304" t="n"/>
@@ -2678,7 +2671,7 @@
       </c>
       <c r="E12" s="313" t="inlineStr">
         <is>
-          <t>처음 열 때 오늘 근처로 시작하고, 연도 확장 시 오른쪽 끝으로 자동 이동하지 않음</t>
+          <t>처음 열 때 오늘 근처로 시작하고, 연도 확장 시 오른쪽 끝으로 자동 이동하지 않음. 2026-07-03 바 드래그/양끝 조절 중 scrollLeft를 고정하고 release 시 같은 위치로 복구하도록 보강.</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2725,7 @@
       </c>
       <c r="E14" s="313" t="inlineStr">
         <is>
-          <t>줄 클릭은 수정창을 열지 않고 해당 간트 바 위치로 이동. 수정은 연필 버튼으로 분리</t>
+          <t>줄 클릭은 수정창을 열지 않고 해당 간트 바 위치로 이동. 수정은 연필 버튼으로 분리. 2026-07-03 panel 내부의 해당 바를 찾아 즉시/다음 프레임 재정렬하도록 보강.</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4745,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="73" t="inlineStr">
         <is>
@@ -7138,7 +7130,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="116" t="inlineStr">
         <is>

--- a/docs/기능_API연결_색상표_2026-07-01.xlsx
+++ b/docs/기능_API연결_색상표_2026-07-01.xlsx
@@ -2393,7 +2393,7 @@
       </c>
       <c r="D1" s="304" t="inlineStr">
         <is>
-          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화, WBS 스크롤/접힘 UX</t>
+          <t>프로젝트룸 WBS/칸반 후보 생성, WBS 생성 UX, Google Calendar 삭제 동기화, WBS 스크롤/접힘 UX, 드래그 스크롤 안정화</t>
         </is>
       </c>
       <c r="E1" s="304" t="n"/>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E12" s="313" t="inlineStr">
         <is>
-          <t>처음 열 때 오늘 근처로 시작하고, 연도 확장 시 오른쪽 끝으로 자동 이동하지 않음</t>
+          <t>처음 열 때 오늘 근처로 시작하고, 연도 확장 시 오른쪽 끝으로 자동 이동하지 않음. 2026-07-03 바 드래그/양끝 조절 중 scrollLeft를 고정하고 release 시 같은 위치로 복구하도록 보강.</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E14" s="313" t="inlineStr">
         <is>
-          <t>줄 클릭은 수정창을 열지 않고 해당 간트 바 위치로 이동. 수정은 연필 버튼으로 분리</t>
+          <t>줄 클릭은 수정창을 열지 않고 해당 간트 바 위치로 이동. 수정은 연필 버튼으로 분리. 2026-07-03 panel 내부의 해당 바를 찾아 즉시/다음 프레임 재정렬하도록 보강.</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="L6" s="25" t="inlineStr">
         <is>
-          <t>세션 refresh·logout 연결. 2026-07-03 작은 창 배경 끊김 Playwright 확인.</t>
+          <t>세션 refresh·logout 연결</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="G6" s="216" t="inlineStr">
         <is>
-          <t>Playwright 확인</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="H6" s="89" t="inlineStr">
         <is>
-          <t>디자인 완료 · 2026-07-03 로그인 배경 끊김 방지. 674x610·674x900·448x563 Playwright 캡처에서 main 높이/배경/콘솔 에러 0 확인. OAuth 호환 라우트는 기존 흐름 유지.</t>
+          <t>디자인 완료 · 반응형 미확인</t>
         </is>
       </c>
     </row>
